--- a/results/表5_水分浓度.xlsx
+++ b/results/表5_水分浓度.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -632,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.75" defaultRowHeight="14.1" customHeight="1"/>
   <cols>
     <col width="19.625" customWidth="1" style="2" min="1" max="1"/>
@@ -647,7 +647,7 @@
     <row r="1" ht="14.1" customHeight="1" s="4">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>时间\到药材中心的距离</t>
+          <t>时间/h\到药材中心的距离/cm</t>
         </is>
       </c>
       <c r="B1" s="1" t="n">
@@ -668,182 +668,204 @@
     </row>
     <row r="2" ht="14.1" customHeight="1" s="4">
       <c r="A2" s="1" t="n">
-        <v>21600</v>
+        <v>6</v>
       </c>
       <c r="B2" s="5" t="n">
-        <v>1.01697</v>
+        <v>1.017</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>0.98813</v>
+        <v>0.9881</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>0.90152</v>
+        <v>0.9015</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0.75501</v>
+        <v>0.755</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>0.53627</v>
+        <v>0.5328000000000001</v>
       </c>
     </row>
     <row r="3" ht="14.1" customHeight="1" s="4">
       <c r="A3" s="1" t="n">
-        <v>43200</v>
+        <v>12</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>0.45615</v>
+        <v>0.4561</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>0.44316</v>
+        <v>0.4432</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>0.40307</v>
+        <v>0.4031</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>0.32973</v>
+        <v>0.3297</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>0.16927</v>
+        <v>0.1642</v>
       </c>
     </row>
     <row r="4" ht="14.1" customHeight="1" s="4">
       <c r="A4" s="1" t="n">
-        <v>64800</v>
+        <v>18</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.29884</v>
+        <v>0.2988</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.29155</v>
+        <v>0.2916</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.26872</v>
+        <v>0.2687</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.22532</v>
+        <v>0.2253</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.09606000000000001</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="5" ht="14.1" customHeight="1" s="4">
       <c r="A5" s="1" t="n">
-        <v>86400</v>
+        <v>24</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.23781</v>
+        <v>0.2378</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.23276</v>
+        <v>0.2328</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.21675</v>
+        <v>0.2168</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.18561</v>
+        <v>0.1856</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.08032</v>
+        <v>0.0664</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>108000</v>
+        <v>30</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.20586</v>
+        <v>0.2059</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.20188</v>
+        <v>0.2019</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.18922</v>
+        <v>0.1892</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.16419</v>
+        <v>0.1642</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.07362</v>
+        <v>0.0598</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>129600</v>
+        <v>36</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.18592</v>
+        <v>0.1859</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.18258</v>
+        <v>0.1826</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.17188</v>
+        <v>0.1719</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.15049</v>
+        <v>0.1505</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.06974</v>
+        <v>0.0566</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>151200</v>
+        <v>42</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.17212</v>
+        <v>0.1721</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.16919</v>
+        <v>0.1692</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.15978</v>
+        <v>0.1598</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.14082</v>
+        <v>0.1408</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.06714000000000001</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>172800</v>
+        <v>48</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.16189</v>
+        <v>0.1619</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.15925</v>
+        <v>0.1593</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.15077</v>
+        <v>0.1508</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.13355</v>
+        <v>0.1336</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.06524000000000001</v>
+        <v>0.0537</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>194400</v>
+        <v>54</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.15393</v>
+        <v>0.1539</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.15152</v>
+        <v>0.1515</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.14372</v>
+        <v>0.1437</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.12783</v>
+        <v>0.1278</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.06376999999999999</v>
+        <v>0.053</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>烘干结束时间=57.5357 h</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.1402</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.0527</v>
       </c>
     </row>
   </sheetData>
